--- a/ops/finanzas/checklist_pagos_argentina.xlsx
+++ b/ops/finanzas/checklist_pagos_argentina.xlsx
@@ -12,7 +12,7 @@
     <sheet name="RESUMEN" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CHECKLIST'!$A$7:$J$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CHECKLIST'!$A$7:$J$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1051,7 +1051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1128,7 +1128,7 @@
     </row>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="13" t="n">
-        <v>242347.2114587086</v>
+        <v>236647.2114587086</v>
       </c>
       <c r="B5" s="6" t="n"/>
       <c r="C5" s="6" t="n"/>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="E5" s="8" t="n"/>
       <c r="F5" s="15" t="n">
-        <v>186456.0614587086</v>
+        <v>180756.0614587086</v>
       </c>
       <c r="G5" s="10" t="n"/>
       <c r="H5" s="16" t="n">
@@ -2442,7 +2442,7 @@
       <c r="H36" s="70" t="n"/>
       <c r="I36" s="70" t="n"/>
       <c r="J36" s="71">
-        <f>SUM(E37:E45)</f>
+        <f>SUM(E37:E40)</f>
         <v/>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="B37" s="73" t="inlineStr">
         <is>
-          <t>Producción</t>
+          <t>Servicios</t>
         </is>
       </c>
       <c r="C37" s="74" t="inlineStr">
@@ -2464,12 +2464,10 @@
       </c>
       <c r="D37" s="75" t="inlineStr">
         <is>
-          <t>Master Mind Hit (sala adicional)</t>
-        </is>
-      </c>
-      <c r="E37" s="76" t="n">
-        <v>3000</v>
-      </c>
+          <t>Ecobaños</t>
+        </is>
+      </c>
+      <c r="E37" s="76" t="n"/>
       <c r="F37" s="77" t="inlineStr">
         <is>
           <t>pedir</t>
@@ -2492,7 +2490,7 @@
       </c>
       <c r="J37" s="78" t="inlineStr">
         <is>
-          <t>Estimado de la planilla, sin cotización.</t>
+          <t>Decidido que van ecobaños. Sin cotizar: hoy entra en cero.</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2502,7 @@
       </c>
       <c r="B38" s="73" t="inlineStr">
         <is>
-          <t>Producción</t>
+          <t>Merch</t>
         </is>
       </c>
       <c r="C38" s="74" t="inlineStr">
@@ -2514,12 +2512,10 @@
       </c>
       <c r="D38" s="75" t="inlineStr">
         <is>
-          <t>Unifilas</t>
-        </is>
-      </c>
-      <c r="E38" s="76" t="n">
-        <v>1200</v>
-      </c>
+          <t>Marquetería y enmarcado</t>
+        </is>
+      </c>
+      <c r="E38" s="76" t="n"/>
       <c r="F38" s="77" t="inlineStr">
         <is>
           <t>pedir</t>
@@ -2542,7 +2538,7 @@
       </c>
       <c r="J38" s="78" t="inlineStr">
         <is>
-          <t>Estimado de la planilla.</t>
+          <t>Certificaciones y premios. Sin cotizar.</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2550,7 @@
       </c>
       <c r="B39" s="73" t="inlineStr">
         <is>
-          <t>Producción</t>
+          <t>Merch</t>
         </is>
       </c>
       <c r="C39" s="74" t="inlineStr">
@@ -2564,12 +2560,10 @@
       </c>
       <c r="D39" s="75" t="inlineStr">
         <is>
-          <t>Escoltas (2)</t>
-        </is>
-      </c>
-      <c r="E39" s="76" t="n">
-        <v>1000</v>
-      </c>
+          <t>Cheques, escarapelas, diplomas, placas y manillas</t>
+        </is>
+      </c>
+      <c r="E39" s="76" t="n"/>
       <c r="F39" s="77" t="inlineStr">
         <is>
           <t>pedir</t>
@@ -2592,7 +2586,7 @@
       </c>
       <c r="J39" s="78" t="inlineStr">
         <is>
-          <t>Estimado de la planilla.</t>
+          <t>Lo único del merch que las facturas no cubren.</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2598,7 @@
       </c>
       <c r="B40" s="73" t="inlineStr">
         <is>
-          <t>Producción</t>
+          <t>Mobiliario</t>
         </is>
       </c>
       <c r="C40" s="74" t="inlineStr">
@@ -2614,12 +2608,10 @@
       </c>
       <c r="D40" s="75" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="E40" s="76" t="n">
-        <v>500</v>
-      </c>
+          <t>Replanteo de sillas con ingeniero</t>
+        </is>
+      </c>
+      <c r="E40" s="76" t="n"/>
       <c r="F40" s="77" t="inlineStr">
         <is>
           <t>pedir</t>
@@ -2642,383 +2634,142 @@
       </c>
       <c r="J40" s="78" t="inlineStr">
         <is>
-          <t>Estimado de la planilla.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="72" t="inlineStr">
+          <t>Va aparte de la dirección técnica de La Rural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   7 · AJUSTE DE CONCILIACIÓN</t>
+        </is>
+      </c>
+      <c r="B41" s="80" t="n"/>
+      <c r="C41" s="80" t="n"/>
+      <c r="D41" s="80" t="n"/>
+      <c r="E41" s="80" t="n"/>
+      <c r="F41" s="80" t="n"/>
+      <c r="G41" s="80" t="n"/>
+      <c r="H41" s="80" t="n"/>
+      <c r="I41" s="80" t="n"/>
+      <c r="J41" s="81">
+        <f>SUM(E42:E42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="82" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="B41" s="73" t="inlineStr">
-        <is>
-          <t>Servicios</t>
-        </is>
-      </c>
-      <c r="C41" s="74" t="inlineStr">
-        <is>
-          <t>A definir</t>
-        </is>
-      </c>
-      <c r="D41" s="75" t="inlineStr">
-        <is>
-          <t>Ecobaños</t>
-        </is>
-      </c>
-      <c r="E41" s="76" t="n"/>
-      <c r="F41" s="77" t="inlineStr">
-        <is>
-          <t>pedir</t>
-        </is>
-      </c>
-      <c r="G41" s="73" t="inlineStr">
+      <c r="B42" s="83" t="inlineStr">
+        <is>
+          <t>Merch</t>
+        </is>
+      </c>
+      <c r="C42" s="84" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H41" s="77" t="inlineStr">
+      <c r="D42" s="85" t="inlineStr">
+        <is>
+          <t>Diferencia de tipo de cambio y saldo de gráfica a confirmar</t>
+        </is>
+      </c>
+      <c r="E42" s="86" t="n">
+        <v>590.59</v>
+      </c>
+      <c r="F42" s="87" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I41" s="77" t="inlineStr">
+      <c r="G42" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J41" s="78" t="inlineStr">
-        <is>
-          <t>Decidido que van ecobaños. Sin cotizar: hoy entra en cero.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="72" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B42" s="73" t="inlineStr">
-        <is>
-          <t>Merch</t>
-        </is>
-      </c>
-      <c r="C42" s="74" t="inlineStr">
-        <is>
-          <t>A definir</t>
-        </is>
-      </c>
-      <c r="D42" s="75" t="inlineStr">
-        <is>
-          <t>Marquetería y enmarcado</t>
-        </is>
-      </c>
-      <c r="E42" s="76" t="n"/>
-      <c r="F42" s="77" t="inlineStr">
-        <is>
-          <t>pedir</t>
-        </is>
-      </c>
-      <c r="G42" s="73" t="inlineStr">
+      <c r="H42" s="87" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H42" s="77" t="inlineStr">
+      <c r="I42" s="87" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I42" s="77" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J42" s="78" t="inlineStr">
-        <is>
-          <t>Certificaciones y premios. Sin cotizar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="72" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B43" s="73" t="inlineStr">
-        <is>
-          <t>Merch</t>
-        </is>
-      </c>
-      <c r="C43" s="74" t="inlineStr">
-        <is>
-          <t>A definir</t>
-        </is>
-      </c>
-      <c r="D43" s="75" t="inlineStr">
-        <is>
-          <t>Cheques, escarapelas, diplomas, placas y manillas</t>
-        </is>
-      </c>
-      <c r="E43" s="76" t="n"/>
-      <c r="F43" s="77" t="inlineStr">
-        <is>
-          <t>pedir</t>
-        </is>
-      </c>
-      <c r="G43" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H43" s="77" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I43" s="77" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J43" s="78" t="inlineStr">
-        <is>
-          <t>Lo único del merch que las facturas no cubren.</t>
+      <c r="J42" s="88" t="inlineStr">
+        <is>
+          <t>Las facturas de merch se emitieron a dólar $1.535 y los pagos de junio se hicieron a $1.475, así que las mitades no suman exacto. El grueso es el saldo de la gráfica de Argentina: el master dice US$1.839 y la factura 2601014 viene por US$2.385.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="72" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B44" s="73" t="inlineStr">
-        <is>
-          <t>Mobiliario</t>
-        </is>
-      </c>
-      <c r="C44" s="74" t="inlineStr">
-        <is>
-          <t>A definir</t>
-        </is>
-      </c>
-      <c r="D44" s="75" t="inlineStr">
-        <is>
-          <t>Replanteo de sillas con ingeniero</t>
-        </is>
-      </c>
-      <c r="E44" s="76" t="n"/>
-      <c r="F44" s="77" t="inlineStr">
-        <is>
-          <t>pedir</t>
-        </is>
-      </c>
-      <c r="G44" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H44" s="77" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I44" s="77" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J44" s="78" t="inlineStr">
-        <is>
-          <t>Va aparte de la dirección técnica de La Rural.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="72" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B45" s="73" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-      <c r="C45" s="74" t="inlineStr">
-        <is>
-          <t>A definir</t>
-        </is>
-      </c>
-      <c r="D45" s="75" t="inlineStr">
-        <is>
-          <t>Vuelos, alojamiento y traslados del equipo (8 personas)</t>
-        </is>
-      </c>
-      <c r="E45" s="76" t="n"/>
-      <c r="F45" s="77" t="inlineStr">
-        <is>
-          <t>pedir</t>
-        </is>
-      </c>
-      <c r="G45" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H45" s="77" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I45" s="77" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J45" s="78" t="inlineStr">
-        <is>
-          <t>El hueco más grande: no hay cotización ni estimado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   7 · AJUSTE DE CONCILIACIÓN</t>
-        </is>
-      </c>
-      <c r="B46" s="80" t="n"/>
-      <c r="C46" s="80" t="n"/>
-      <c r="D46" s="80" t="n"/>
-      <c r="E46" s="80" t="n"/>
-      <c r="F46" s="80" t="n"/>
-      <c r="G46" s="80" t="n"/>
-      <c r="H46" s="80" t="n"/>
-      <c r="I46" s="80" t="n"/>
-      <c r="J46" s="81">
-        <f>SUM(E47:E47)</f>
+      <c r="A44" s="89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   TOTAL A DESEMBOLSAR</t>
+        </is>
+      </c>
+      <c r="B44" s="90" t="n"/>
+      <c r="C44" s="90" t="n"/>
+      <c r="D44" s="90" t="n"/>
+      <c r="E44" s="91">
+        <f>J8+J12+J15+J25+J30+J36+J41</f>
         <v/>
       </c>
-    </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="82" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B47" s="83" t="inlineStr">
-        <is>
-          <t>Merch</t>
-        </is>
-      </c>
-      <c r="C47" s="84" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D47" s="85" t="inlineStr">
-        <is>
-          <t>Diferencia de tipo de cambio y saldo de gráfica a confirmar</t>
-        </is>
-      </c>
-      <c r="E47" s="86" t="n">
-        <v>590.59</v>
-      </c>
-      <c r="F47" s="87" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G47" s="83" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H47" s="87" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I47" s="87" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J47" s="88" t="inlineStr">
-        <is>
-          <t>Las facturas de merch se emitieron a dólar $1.535 y los pagos de junio se hicieron a $1.475, así que las mitades no suman exacto. El grueso es el saldo de la gráfica de Argentina: el master dice US$1.839 y la factura 2601014 viene por US$2.385.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   TOTAL A DESEMBOLSAR</t>
-        </is>
-      </c>
-      <c r="B49" s="90" t="n"/>
-      <c r="C49" s="90" t="n"/>
-      <c r="D49" s="90" t="n"/>
-      <c r="E49" s="91">
-        <f>J8+J12+J15+J25+J30+J36+J46</f>
-        <v/>
-      </c>
-      <c r="F49" s="90" t="n"/>
-      <c r="G49" s="90" t="n"/>
-      <c r="H49" s="90" t="n"/>
-      <c r="I49" s="90" t="n"/>
-      <c r="J49" s="90" t="n"/>
-    </row>
-    <row r="51">
-      <c r="B51" s="92" t="inlineStr">
+      <c r="F44" s="90" t="n"/>
+      <c r="G44" s="90" t="n"/>
+      <c r="H44" s="90" t="n"/>
+      <c r="I44" s="90" t="n"/>
+      <c r="J44" s="90" t="n"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="92" t="inlineStr">
         <is>
           <t>Marcá la columna ✔ a medida que salen los pagos: la fila se pinta de verde sola.</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="92" t="inlineStr">
+    <row r="47">
+      <c r="B47" s="92" t="inlineStr">
         <is>
           <t>Los tramos están ordenados por urgencia. El 1 es lo vencido o ya facturado; el 2, los anticipos del 50% que destraban técnica y catering.</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" s="92" t="inlineStr">
+    <row r="48">
+      <c r="B48" s="92" t="inlineStr">
         <is>
           <t>Los pagos de merch van en USDT por red BEP20. Remerasyestampados: 0xae874c3db52ca1e45604549a5527f450a877b97a · Leotex y Derqui: 0x7d0a6c347008305af1d6643c2382e1495af7dc0e. Verificá la dirección con el proveedor antes de operar.</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="92" t="inlineStr">
+    <row r="49">
+      <c r="B49" s="92" t="inlineStr">
         <is>
           <t>FDL Eventos y Vittal todavía no confirmaron si pueden facturar a la empresa de EE.UU.: son US$25.333 trabados por un tema administrativo.</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" s="92" t="inlineStr">
+    <row r="50">
+      <c r="B50" s="92" t="inlineStr">
         <is>
           <t>Higia pide 50% de anticipo antes del armado y Gale factura el 100% por adelantado.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:J47"/>
+  <autoFilter ref="A7:J42"/>
   <mergeCells count="18">
     <mergeCell ref="A15:I15"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A46:I46"/>
     <mergeCell ref="H5:J5"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="D5:E5"/>
@@ -3030,14 +2781,15 @@
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A44:D44"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:J47">
+  <conditionalFormatting sqref="A8:J42">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$A8="✔"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A9 A10 A11 A13 A14 A16 A17 A18 A19 A20 A21 A22 A23 A24 A26 A27 A28 A29 A31 A32 A33 A34 A35 A37 A38 A39 A40 A41 A42 A43 A44 A45 A47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A9 A10 A11 A13 A14 A16 A17 A18 A19 A20 A21 A22 A23 A24 A26 A27 A28 A29 A31 A32 A33 A34 A35 A37 A38 A39 A40 A42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"☐,✔"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3594,7 +3346,7 @@
         </is>
       </c>
       <c r="B10" s="124">
-        <f>CHECKLIST!J46</f>
+        <f>CHECKLIST!J41</f>
         <v/>
       </c>
       <c r="C10" s="125">
